--- a/data/trans_orig/Q47-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Q47-Provincia-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según su talla</t>
+          <t>Población según su talla (tasa de respuesta: 98,01%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>172,73; 174,37</t>
+          <t>172,71; 174,38</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>172,57; 174,48</t>
+          <t>172,54; 174,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>173,32; 175,16</t>
+          <t>173,23; 175,14</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>174,07; 176,9</t>
+          <t>174,0; 176,93</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>160,52; 162,03</t>
+          <t>160,58; 162,16</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>160,09; 161,77</t>
+          <t>160,09; 161,8</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>160,84; 162,42</t>
+          <t>160,78; 162,41</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>161,11; 162,34</t>
+          <t>161,11; 162,36</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>166,8; 168,32</t>
+          <t>166,78; 168,36</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>166,57; 168,32</t>
+          <t>166,62; 168,26</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>167,21; 168,92</t>
+          <t>167,23; 168,91</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>167,75; 169,8</t>
+          <t>167,73; 169,92</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>171,86; 173,18</t>
+          <t>171,89; 173,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>172,05; 173,37</t>
+          <t>172,02; 173,41</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>171,5; 172,87</t>
+          <t>171,56; 172,91</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>172,54; 173,98</t>
+          <t>172,44; 174,01</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>159,74; 160,91</t>
+          <t>159,73; 160,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>160,17; 161,46</t>
+          <t>160,08; 161,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>159,92; 161,15</t>
+          <t>159,88; 161,1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>161,73; 162,77</t>
+          <t>161,75; 162,76</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>165,76; 166,93</t>
+          <t>165,84; 167,01</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>166,05; 167,29</t>
+          <t>166,03; 167,27</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>165,68; 166,92</t>
+          <t>165,77; 166,93</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>167,28; 168,49</t>
+          <t>167,18; 168,41</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>171,94; 173,66</t>
+          <t>172,0; 173,72</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>172,29; 173,79</t>
+          <t>172,31; 173,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>173,4; 175,02</t>
+          <t>173,47; 175,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>172,51; 174,37</t>
+          <t>172,44; 174,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>159,65; 161,16</t>
+          <t>159,67; 161,12</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>160,53; 161,89</t>
+          <t>160,51; 161,86</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>161,19; 162,7</t>
+          <t>161,19; 162,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>160,77; 161,92</t>
+          <t>160,77; 161,9</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>165,8; 167,28</t>
+          <t>165,72; 167,3</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>166,33; 167,73</t>
+          <t>166,28; 167,64</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>167,23; 168,75</t>
+          <t>167,23; 168,7</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>166,46; 167,88</t>
+          <t>166,45; 167,79</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>172,99; 174,63</t>
+          <t>173,01; 174,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>171,94; 173,72</t>
+          <t>172,12; 173,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>172,43; 174,08</t>
+          <t>172,5; 174,12</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>172,77; 174,54</t>
+          <t>172,76; 174,54</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>161,03; 162,43</t>
+          <t>161,04; 162,43</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>160,51; 161,95</t>
+          <t>160,42; 161,95</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>160,51; 161,9</t>
+          <t>160,56; 161,95</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>157,17; 162,16</t>
+          <t>157,22; 162,09</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>167,02; 168,32</t>
+          <t>166,96; 168,26</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>166,5; 167,94</t>
+          <t>166,46; 167,94</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>166,62; 168,08</t>
+          <t>166,66; 168,12</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>162,47; 167,62</t>
+          <t>162,32; 167,68</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>171,19; 173,2</t>
+          <t>171,19; 173,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>172,93; 174,98</t>
+          <t>172,89; 175,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>171,83; 173,75</t>
+          <t>171,85; 173,7</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>175,7; 177,38</t>
+          <t>175,75; 177,43</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>159,97; 161,96</t>
+          <t>159,97; 161,84</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>159,32; 161,39</t>
+          <t>159,52; 161,43</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>160,33; 161,89</t>
+          <t>160,33; 161,9</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>162,82; 163,87</t>
+          <t>162,79; 163,79</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>165,67; 167,46</t>
+          <t>165,6; 167,36</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>166,19; 168,18</t>
+          <t>166,25; 168,21</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>165,93; 167,69</t>
+          <t>165,94; 167,68</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>168,72; 170,18</t>
+          <t>168,76; 170,25</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>172,75; 174,48</t>
+          <t>172,67; 174,35</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>172,65; 174,47</t>
+          <t>172,55; 174,4</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>172,26; 174,05</t>
+          <t>172,24; 174,08</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>171,38; 173,01</t>
+          <t>171,46; 173,08</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>159,18; 160,77</t>
+          <t>159,19; 160,82</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>160,06; 161,67</t>
+          <t>160,03; 161,73</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>159,69; 161,21</t>
+          <t>159,73; 161,34</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>161,18; 162,65</t>
+          <t>161,13; 162,58</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>165,87; 167,54</t>
+          <t>165,75; 167,48</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>166,23; 167,97</t>
+          <t>166,32; 167,98</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>165,95; 167,62</t>
+          <t>165,92; 167,47</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>166,6; 167,96</t>
+          <t>166,54; 167,92</t>
         </is>
       </c>
     </row>
@@ -1561,57 +1561,57 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>172,97; 174,08</t>
+          <t>172,94; 174,12</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>175,82; 177,2</t>
+          <t>175,93; 177,09</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>173,53; 174,85</t>
+          <t>173,48; 174,75</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>160,62; 161,76</t>
+          <t>160,62; 161,75</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>161,1; 162,17</t>
+          <t>161,16; 162,19</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>162,2; 163,25</t>
+          <t>162,25; 163,3</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>157,62; 162,23</t>
+          <t>157,5; 162,2</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>166,68; 167,73</t>
+          <t>166,65; 167,77</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>166,89; 167,95</t>
+          <t>166,92; 167,99</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>168,88; 170,05</t>
+          <t>168,85; 170,02</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>161,79; 168,12</t>
+          <t>161,8; 168,22</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>172,61; 173,68</t>
+          <t>172,58; 173,72</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>172,08; 173,25</t>
+          <t>172,08; 173,28</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>172,62; 173,74</t>
+          <t>172,71; 173,79</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>172,92; 179,06</t>
+          <t>172,91; 178,89</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>160,53; 161,51</t>
+          <t>160,61; 161,52</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>160,34; 161,23</t>
+          <t>160,34; 161,22</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>160,74; 161,72</t>
+          <t>160,69; 161,8</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>161,42; 162,58</t>
+          <t>161,35; 162,56</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>166,5; 167,43</t>
+          <t>166,45; 167,46</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>166,09; 167,01</t>
+          <t>166,07; 167,04</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>166,52; 167,49</t>
+          <t>166,52; 167,53</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>167,36; 174,39</t>
+          <t>167,33; 174,61</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1836,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>172,92; 173,42</t>
+          <t>172,92; 173,44</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>172,87; 173,39</t>
+          <t>172,83; 173,39</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>173,59; 174,13</t>
+          <t>173,58; 174,1</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>173,64; 176,03</t>
+          <t>173,63; 176,17</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>160,65; 161,11</t>
+          <t>160,69; 161,12</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>160,78; 161,26</t>
+          <t>160,83; 161,28</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>161,22; 161,71</t>
+          <t>161,22; 161,69</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>160,25; 162,02</t>
+          <t>159,95; 162,0</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>166,72; 167,18</t>
+          <t>166,72; 167,19</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>166,78; 167,24</t>
+          <t>166,79; 167,25</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>167,32; 167,8</t>
+          <t>167,32; 167,79</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>166,73; 169,32</t>
+          <t>166,77; 169,25</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q47-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Q47-Provincia-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>175,23</t>
+          <t>174,98</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>161,71</t>
+          <t>161,73</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>168,72</t>
+          <t>168,38</t>
         </is>
       </c>
     </row>
@@ -716,27 +716,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>172,71; 174,38</t>
+          <t>172,78; 174,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>172,54; 174,48</t>
+          <t>172,63; 174,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>173,23; 175,14</t>
+          <t>173,3; 175,08</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>174,0; 176,93</t>
+          <t>174,02; 175,99</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>160,58; 162,16</t>
+          <t>160,5; 161,99</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -746,32 +746,32 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>160,78; 162,41</t>
+          <t>160,73; 162,43</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>161,11; 162,36</t>
+          <t>161,15; 162,29</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>166,78; 168,36</t>
+          <t>166,72; 168,3</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>166,62; 168,26</t>
+          <t>166,54; 168,23</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>167,23; 168,91</t>
+          <t>167,21; 168,87</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>167,73; 169,92</t>
+          <t>167,62; 169,17</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>173,21</t>
+          <t>173,22</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>162,26</t>
+          <t>162,23</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>167,82</t>
+          <t>167,72</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>171,89; 173,14</t>
+          <t>171,9; 173,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>172,02; 173,41</t>
+          <t>172,05; 173,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>171,56; 172,91</t>
+          <t>171,49; 172,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>172,44; 174,01</t>
+          <t>172,48; 173,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>159,73; 160,87</t>
+          <t>159,75; 160,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>160,08; 161,39</t>
+          <t>160,06; 161,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>159,88; 161,1</t>
+          <t>159,84; 161,13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>161,75; 162,76</t>
+          <t>161,68; 162,76</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>165,84; 167,01</t>
+          <t>165,76; 166,97</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>166,03; 167,27</t>
+          <t>166,08; 167,34</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>165,77; 166,93</t>
+          <t>165,68; 166,92</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>167,18; 168,41</t>
+          <t>167,1; 168,27</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>173,42</t>
+          <t>173,48</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>161,31</t>
+          <t>161,24</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>167,13</t>
+          <t>167,06</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>172,0; 173,72</t>
+          <t>172,02; 173,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>172,31; 173,8</t>
+          <t>172,37; 173,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>173,47; 175,05</t>
+          <t>173,45; 175,03</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>172,44; 174,31</t>
+          <t>172,59; 174,39</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>159,67; 161,12</t>
+          <t>159,63; 161,16</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>160,51; 161,86</t>
+          <t>160,46; 161,88</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>161,19; 162,74</t>
+          <t>161,13; 162,69</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>160,77; 161,9</t>
+          <t>160,71; 161,81</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>165,72; 167,3</t>
+          <t>165,75; 167,25</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>166,28; 167,64</t>
+          <t>166,3; 167,67</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>167,23; 168,7</t>
+          <t>167,27; 168,68</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>166,45; 167,79</t>
+          <t>166,39; 167,71</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>173,67</t>
+          <t>173,85</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>160,42</t>
+          <t>161,95</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>165,97</t>
+          <t>167,61</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>173,01; 174,56</t>
+          <t>172,99; 174,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>172,12; 173,79</t>
+          <t>172,13; 173,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>172,5; 174,12</t>
+          <t>172,43; 174,05</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>172,76; 174,54</t>
+          <t>172,88; 174,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>161,04; 162,43</t>
+          <t>161,0; 162,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>160,42; 161,95</t>
+          <t>160,43; 161,92</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>160,56; 161,95</t>
+          <t>160,5; 161,89</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>157,22; 162,09</t>
+          <t>161,37; 162,68</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>166,96; 168,26</t>
+          <t>166,96; 168,33</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>166,46; 167,94</t>
+          <t>166,48; 167,93</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>166,66; 168,12</t>
+          <t>166,63; 168,09</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>162,32; 167,68</t>
+          <t>166,87; 168,44</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>176,58</t>
+          <t>176,47</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>163,33</t>
+          <t>163,38</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>169,47</t>
+          <t>169,61</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>171,19; 173,3</t>
+          <t>171,19; 173,23</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>172,89; 175,0</t>
+          <t>172,87; 174,97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>171,85; 173,7</t>
+          <t>171,8; 173,7</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>175,75; 177,43</t>
+          <t>175,65; 177,29</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>159,97; 161,84</t>
+          <t>159,99; 161,78</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>159,52; 161,43</t>
+          <t>159,46; 161,39</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>160,33; 161,9</t>
+          <t>160,25; 161,9</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>162,79; 163,79</t>
+          <t>162,89; 163,92</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>165,6; 167,36</t>
+          <t>165,65; 167,44</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>166,25; 168,21</t>
+          <t>166,29; 168,19</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>165,94; 167,68</t>
+          <t>165,98; 167,66</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>168,76; 170,25</t>
+          <t>168,86; 170,32</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>172,22</t>
+          <t>172,13</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>161,88</t>
+          <t>161,92</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>167,25</t>
+          <t>167,17</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>172,67; 174,35</t>
+          <t>172,7; 174,42</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>172,55; 174,4</t>
+          <t>172,52; 174,45</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>172,24; 174,08</t>
+          <t>172,09; 174,1</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>171,46; 173,08</t>
+          <t>171,35; 172,96</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>159,19; 160,82</t>
+          <t>159,03; 160,8</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>160,03; 161,73</t>
+          <t>160,07; 161,73</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>159,73; 161,34</t>
+          <t>159,68; 161,19</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>161,13; 162,58</t>
+          <t>161,21; 162,67</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>165,75; 167,48</t>
+          <t>165,88; 167,55</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>166,32; 167,98</t>
+          <t>166,35; 168,05</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>165,92; 167,47</t>
+          <t>165,92; 167,55</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>166,54; 167,92</t>
+          <t>166,47; 167,78</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>174,1</t>
+          <t>173,98</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>160,34</t>
+          <t>162,04</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>166,18</t>
+          <t>167,81</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>172,91; 174,11</t>
+          <t>172,93; 174,15</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>172,94; 174,12</t>
+          <t>172,92; 174,1</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>175,93; 177,09</t>
+          <t>175,83; 177,13</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>173,48; 174,75</t>
+          <t>173,37; 174,64</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>160,62; 161,75</t>
+          <t>160,6; 161,77</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>161,16; 162,19</t>
+          <t>161,1; 162,2</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>162,25; 163,3</t>
+          <t>162,27; 163,32</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>157,5; 162,2</t>
+          <t>161,59; 162,52</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>166,65; 167,77</t>
+          <t>166,64; 167,81</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>166,92; 167,99</t>
+          <t>166,96; 168,08</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>168,85; 170,02</t>
+          <t>168,85; 170,01</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>161,8; 168,22</t>
+          <t>167,29; 168,3</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>175,43</t>
+          <t>173,14</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>162,14</t>
+          <t>162,34</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>169,68</t>
+          <t>167,66</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>172,58; 173,72</t>
+          <t>172,61; 173,73</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>172,08; 173,28</t>
+          <t>172,11; 173,29</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>172,71; 173,79</t>
+          <t>172,67; 173,77</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>172,91; 178,89</t>
+          <t>172,62; 173,65</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>160,61; 161,52</t>
+          <t>160,55; 161,52</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>160,34; 161,22</t>
+          <t>160,29; 161,19</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>160,69; 161,8</t>
+          <t>160,77; 161,7</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>161,35; 162,56</t>
+          <t>161,96; 162,69</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>166,45; 167,46</t>
+          <t>166,42; 167,41</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>166,07; 167,04</t>
+          <t>166,12; 167,0</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>166,52; 167,53</t>
+          <t>166,55; 167,48</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>167,33; 174,61</t>
+          <t>167,28; 168,08</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>174,31</t>
+          <t>173,71</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>161,47</t>
+          <t>162,1</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>167,79</t>
+          <t>167,78</t>
         </is>
       </c>
     </row>
@@ -1836,47 +1836,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>172,92; 173,44</t>
+          <t>172,91; 173,42</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>172,83; 173,39</t>
+          <t>172,85; 173,38</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>173,58; 174,1</t>
+          <t>173,58; 174,12</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>173,63; 176,17</t>
+          <t>173,47; 173,98</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>160,69; 161,12</t>
+          <t>160,66; 161,13</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>160,83; 161,28</t>
+          <t>160,78; 161,24</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>161,22; 161,69</t>
+          <t>161,21; 161,68</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>159,95; 162,0</t>
+          <t>161,91; 162,28</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>166,72; 167,19</t>
+          <t>166,73; 167,16</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>167,32; 167,79</t>
+          <t>167,28; 167,77</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>166,77; 169,25</t>
+          <t>167,54; 168,0</t>
         </is>
       </c>
     </row>
